--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ47"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4160,10 +4160,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119016733</v>
+        <v>136854186</v>
       </c>
       <c r="B36" t="n">
-        <v>57953</v>
+        <v>80095</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4171,39 +4171,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Berg, Hjd</t>
+          <t>Lövnäset, Lövnäset, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>403343</v>
+        <v>403420</v>
       </c>
       <c r="R36" t="n">
-        <v>6961581</v>
+        <v>6961691</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4230,12 +4225,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4250,24 +4245,24 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119016733</t>
+          <t>https://artportalen.se/Sighting/136854186</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119017080</v>
+        <v>119016733</v>
       </c>
       <c r="B37" t="n">
         <v>57953</v>
@@ -4298,7 +4293,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4307,10 +4302,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>403424</v>
+        <v>403343</v>
       </c>
       <c r="R37" t="n">
-        <v>6961596</v>
+        <v>6961581</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4368,13 +4363,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119017080</t>
+          <t>https://artportalen.se/Sighting/119016733</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119017698</v>
+        <v>119017080</v>
       </c>
       <c r="B38" t="n">
         <v>57953</v>
@@ -4405,7 +4400,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4414,13 +4409,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>403235</v>
+        <v>403424</v>
       </c>
       <c r="R38" t="n">
-        <v>6961455</v>
+        <v>6961596</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4450,11 +4445,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Troligt bo tretåig hackspett</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4480,13 +4470,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119017698</t>
+          <t>https://artportalen.se/Sighting/119017080</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119620790</v>
+        <v>119017698</v>
       </c>
       <c r="B39" t="n">
         <v>57953</v>
@@ -4514,32 +4504,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storbäcken, Storsjö, Hjd</t>
+          <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>403339</v>
+        <v>403235</v>
       </c>
       <c r="R39" t="n">
-        <v>6961635</v>
+        <v>6961455</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4563,22 +4546,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Troligt bo tretåig hackspett</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4589,76 +4567,78 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Stefan Dahlsten</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Stefan Dahlsten</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119620790</t>
+          <t>https://artportalen.se/Sighting/119017698</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119015582</v>
+        <v>119620790</v>
       </c>
       <c r="B40" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Berg, Hjd</t>
+          <t>Storbäcken, Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>403481</v>
+        <v>403339</v>
       </c>
       <c r="R40" t="n">
-        <v>6961646</v>
+        <v>6961635</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4685,12 +4665,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4701,73 +4691,79 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Stefan Dahlsten</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Stefan Dahlsten</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119015582</t>
+          <t>https://artportalen.se/Sighting/119620790</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119024388</v>
+        <v>136854175</v>
       </c>
       <c r="B41" t="n">
-        <v>97983</v>
+        <v>58008</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Storbäcken Storsjö, Storsjö, Hjd</t>
+          <t>Lövnäset, Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>403507</v>
+        <v>403413</v>
       </c>
       <c r="R41" t="n">
-        <v>6961648</v>
+        <v>6961666</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4791,12 +4787,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4805,72 +4806,76 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119024388</t>
+          <t>https://artportalen.se/Sighting/136854175</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119015113</v>
+        <v>136854245</v>
       </c>
       <c r="B42" t="n">
-        <v>99140</v>
+        <v>58008</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Berg, Hjd</t>
+          <t>Lövnäset, Lövnäset, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>403485</v>
+        <v>403455</v>
       </c>
       <c r="R42" t="n">
-        <v>6961755</v>
+        <v>6961651</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4894,12 +4899,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4914,27 +4924,27 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119015113</t>
+          <t>https://artportalen.se/Sighting/136854245</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119015364</v>
+        <v>119015582</v>
       </c>
       <c r="B43" t="n">
-        <v>99140</v>
+        <v>57141</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4942,37 +4952,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>403561</v>
+        <v>403481</v>
       </c>
       <c r="R43" t="n">
-        <v>6961727</v>
+        <v>6961646</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5027,16 +5042,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119015364</t>
+          <t>https://artportalen.se/Sighting/119015582</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119017171</v>
+        <v>119024388</v>
       </c>
       <c r="B44" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5044,37 +5059,41 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Berg, Hjd</t>
+          <t>Storbäcken Storsjö, Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>403389</v>
+        <v>403507</v>
       </c>
       <c r="R44" t="n">
-        <v>6961557</v>
+        <v>6961648</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5112,6 +5131,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5129,13 +5149,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119017171</t>
+          <t>https://artportalen.se/Sighting/119024388</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119024259</v>
+        <v>119015113</v>
       </c>
       <c r="B45" t="n">
         <v>99140</v>
@@ -5164,23 +5184,19 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Storbäcken Storsjö, Storsjö, Hjd</t>
+          <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>403532</v>
+        <v>403485</v>
       </c>
       <c r="R45" t="n">
-        <v>6961654</v>
+        <v>6961755</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5218,7 +5234,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5236,38 +5251,38 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119024259</t>
+          <t>https://artportalen.se/Sighting/119015113</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119016397</v>
+        <v>119015364</v>
       </c>
       <c r="B46" t="n">
-        <v>79917</v>
+        <v>99140</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5277,10 +5292,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>403265</v>
+        <v>403561</v>
       </c>
       <c r="R46" t="n">
-        <v>6961667</v>
+        <v>6961727</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5338,38 +5353,38 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119016397</t>
+          <t>https://artportalen.se/Sighting/119015364</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119018628</v>
+        <v>119017171</v>
       </c>
       <c r="B47" t="n">
-        <v>79350</v>
+        <v>99140</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>260591</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5379,10 +5394,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>403409</v>
+        <v>403389</v>
       </c>
       <c r="R47" t="n">
-        <v>6961770</v>
+        <v>6961557</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5439,6 +5454,317 @@
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119017171</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>119024259</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Storbäcken Storsjö, Storsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>403532</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6961654</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119024259</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>119016397</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Berg, Hjd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>403265</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6961667</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119016397</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>119018628</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Berg, Hjd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>403409</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6961770</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119018628</t>
         </is>
@@ -5492,6 +5818,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -4163,7 +4163,7 @@
         <v>136854186</v>
       </c>
       <c r="B36" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -4163,7 +4163,7 @@
         <v>136854186</v>
       </c>
       <c r="B36" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -4163,7 +4163,7 @@
         <v>136854186</v>
       </c>
       <c r="B36" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -4163,7 +4163,7 @@
         <v>136854186</v>
       </c>
       <c r="B36" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -4163,7 +4163,7 @@
         <v>136854186</v>
       </c>
       <c r="B36" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -4163,7 +4163,7 @@
         <v>136854186</v>
       </c>
       <c r="B36" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136854175</v>
       </c>
       <c r="B41" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136854245</v>
       </c>
       <c r="B42" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -4163,7 +4163,7 @@
         <v>136854186</v>
       </c>
       <c r="B36" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136854175</v>
       </c>
       <c r="B41" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136854245</v>
       </c>
       <c r="B42" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -4746,11 +4746,7 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lövnäset, Storsjö, Hjd</t>
@@ -4858,11 +4854,7 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lövnäset, Lövnäset, Hjd</t>

--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -4163,7 +4163,7 @@
         <v>136854186</v>
       </c>
       <c r="B36" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136854175</v>
       </c>
       <c r="B41" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>136854245</v>
       </c>
       <c r="B42" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -4163,7 +4163,7 @@
         <v>136854186</v>
       </c>
       <c r="B36" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136854175</v>
       </c>
       <c r="B41" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>136854245</v>
       </c>
       <c r="B42" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -4163,7 +4163,7 @@
         <v>136854186</v>
       </c>
       <c r="B36" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136854175</v>
       </c>
       <c r="B41" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>136854245</v>
       </c>
       <c r="B42" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -4163,7 +4163,7 @@
         <v>136854186</v>
       </c>
       <c r="B36" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
